--- a/excel_template/수령증양식.xlsx
+++ b/excel_template/수령증양식.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gimdonghun/Documents/DbTest/excel_template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE5F69A-2FB4-274C-A2CD-0440A6496DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2523503B-A01F-DF4A-9C56-FAC8E9339860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="수령증" sheetId="2" r:id="rId1"/>
@@ -52,7 +52,8 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="굴림체"/>
-        <charset val="134"/>
+        <family val="2"/>
+        <charset val="129"/>
       </rPr>
       <t>현금 지급금액(付款金</t>
     </r>
@@ -72,7 +73,8 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="굴림체"/>
-        <charset val="134"/>
+        <family val="2"/>
+        <charset val="129"/>
       </rPr>
       <t>）</t>
     </r>
@@ -85,18 +87,6 @@
   </si>
   <si>
     <t>수령자(收款人签字）：                  （인)</t>
-  </si>
-  <si>
-    <t>原日期</t>
-  </si>
-  <si>
-    <t>姓名</t>
-  </si>
-  <si>
-    <t>品牌</t>
-  </si>
-  <si>
-    <t>SKU</t>
   </si>
   <si>
     <t>REF NO</t>
@@ -130,7 +120,8 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="굴림체"/>
-        <charset val="134"/>
+        <family val="2"/>
+        <charset val="129"/>
       </rPr>
       <t>照</t>
     </r>
@@ -150,7 +141,8 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="굴림체"/>
-        <charset val="134"/>
+        <family val="2"/>
+        <charset val="129"/>
       </rPr>
       <t>）</t>
     </r>
@@ -171,7 +163,8 @@
         <sz val="18"/>
         <color theme="1"/>
         <rFont val="BatangChe"/>
-        <charset val="134"/>
+        <family val="1"/>
+        <charset val="129"/>
       </rPr>
       <t>월</t>
     </r>
@@ -191,7 +184,8 @@
         <sz val="18"/>
         <color theme="1"/>
         <rFont val="BatangChe"/>
-        <charset val="134"/>
+        <family val="1"/>
+        <charset val="129"/>
       </rPr>
       <t>수수료</t>
     </r>
@@ -211,16 +205,14 @@
         <sz val="18"/>
         <color theme="1"/>
         <rFont val="BatangChe"/>
-        <charset val="134"/>
+        <family val="1"/>
+        <charset val="129"/>
       </rPr>
       <t>수령증</t>
     </r>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>免</t>
-    </r>
     <r>
       <rPr>
         <b/>
@@ -230,7 +222,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>税</t>
+      <t>总卖</t>
     </r>
     <r>
       <rPr>
@@ -242,13 +234,10 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>店</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>免</t>
-    </r>
+      <t>出(￦)</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -258,7 +247,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>税</t>
+      <t>纯卖</t>
     </r>
     <r>
       <rPr>
@@ -270,7 +259,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>分店</t>
+      <t>出($)</t>
     </r>
   </si>
   <si>
@@ -283,7 +272,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>购买</t>
+      <t>纯卖</t>
     </r>
     <r>
       <rPr>
@@ -295,10 +284,13 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>日期</t>
-    </r>
-  </si>
-  <si>
+      <t>出(￦)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>点</t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -308,10 +300,13 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>团号</t>
-    </r>
-  </si>
-  <si>
+      <t>数</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>返点金</t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -321,272 +316,68 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>护</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF5F5F5F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>照</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF5F5F5F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>号</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>小票</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF5F5F5F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>号</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>原小票</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF5F5F5F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>号</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>分</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF5F5F5F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>类</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF5F5F5F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>产</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF5F5F5F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>品名</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF5F5F5F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>称</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF5F5F5F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>数</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF5F5F5F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>量</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF5F5F5F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>总卖</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF5F5F5F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>出($)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF5F5F5F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>总卖</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF5F5F5F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>出(￦)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF5F5F5F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>纯卖</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF5F5F5F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>出($)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF5F5F5F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>纯卖</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF5F5F5F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>出(￦)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>点</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF5F5F5F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>数</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>返点金</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF5F5F5F"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>额</t>
     </r>
+  </si>
+  <si>
+    <t>면세점</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>점구분</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>매출일자</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>원매출일자</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>단체번호</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>고객명</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>여권번호</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>교환권번호</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>교환권상태</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>카테고리</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>브랜드</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>상품코드</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>상품명</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>판매수량</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>판매가($)</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -599,7 +390,7 @@
     <numFmt numFmtId="178" formatCode="#,##0_ "/>
     <numFmt numFmtId="179" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -619,7 +410,8 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="굴림체"/>
-      <charset val="134"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
@@ -633,28 +425,32 @@
       <sz val="18"/>
       <color theme="1"/>
       <name val="굴림체"/>
-      <charset val="134"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="굴림체"/>
-      <charset val="134"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="굴림체"/>
-      <charset val="134"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color theme="1"/>
       <name val="BatangChe"/>
-      <charset val="134"/>
+      <family val="1"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
@@ -667,7 +463,8 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
-      <charset val="134"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -717,6 +514,14 @@
       <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF5F5F5F"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="4">
@@ -845,7 +650,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -946,6 +751,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1452,7 +1269,7 @@
   <sheetData>
     <row r="4" spans="2:4" ht="32" customHeight="1">
       <c r="B4" s="30" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C4" s="31"/>
       <c r="D4" s="31"/>
@@ -1481,14 +1298,14 @@
     <row r="8" spans="2:4" ht="56" customHeight="1">
       <c r="B8" s="28"/>
       <c r="C8" s="8" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D8" s="5"/>
     </row>
     <row r="9" spans="2:4" ht="56" customHeight="1">
       <c r="B9" s="29"/>
       <c r="C9" s="9" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D9" s="5"/>
     </row>
@@ -1530,7 +1347,7 @@
     </row>
     <row r="16" spans="2:4" ht="24" customHeight="1">
       <c r="B16" s="25" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C16" s="26"/>
       <c r="D16" s="26"/>
@@ -1578,28 +1395,25 @@
   <dimension ref="A1:AE25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.83203125" style="15" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" style="15" customWidth="1"/>
-    <col min="3" max="4" width="9.6640625" style="15" customWidth="1"/>
-    <col min="5" max="5" width="8.33203125" style="15" customWidth="1"/>
-    <col min="6" max="6" width="9.1640625" style="15" customWidth="1"/>
-    <col min="7" max="7" width="4.33203125" style="15" customWidth="1"/>
-    <col min="8" max="8" width="12.1640625" style="15" customWidth="1"/>
-    <col min="9" max="9" width="3" style="15" customWidth="1"/>
-    <col min="10" max="10" width="9.33203125" style="15" customWidth="1"/>
-    <col min="11" max="11" width="12.1640625" style="15" customWidth="1"/>
-    <col min="12" max="12" width="10.1640625" style="15" customWidth="1"/>
-    <col min="13" max="13" width="6.5" style="15" customWidth="1"/>
-    <col min="14" max="14" width="9.1640625" style="15" customWidth="1"/>
-    <col min="15" max="15" width="4.33203125" style="15" customWidth="1"/>
-    <col min="16" max="16" width="8" style="15" customWidth="1"/>
-    <col min="17" max="17" width="8.6640625" style="15" customWidth="1"/>
-    <col min="18" max="18" width="8" style="15" customWidth="1"/>
-    <col min="19" max="19" width="8.6640625" style="15" customWidth="1"/>
-    <col min="20" max="20" width="5.6640625" style="15" customWidth="1"/>
-    <col min="21" max="22" width="6.33203125" style="15" customWidth="1"/>
-    <col min="23" max="23" width="8.83203125" style="23" customWidth="1"/>
-    <col min="24" max="24" width="12.83203125" style="15" customWidth="1"/>
+    <col min="1" max="2" width="6.5" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8" style="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="6.5" style="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" style="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="5" style="15" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8" style="15" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.5" style="15" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5" style="15" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.5" style="15" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9" style="15" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.5" style="15" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9" style="15" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6" style="15" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.6640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.5" style="15" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5" style="23" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8" style="15" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="13.6640625" style="15" customWidth="1"/>
     <col min="26" max="26" width="10.33203125" style="15"/>
     <col min="27" max="16384" width="9" style="15"/>
@@ -1607,76 +1421,76 @@
   <sheetData>
     <row r="1" spans="1:31" s="24" customFormat="1" ht="33" customHeight="1">
       <c r="A1" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="O1" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="P1" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q1" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="U1" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="V1" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="W1" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="X1" s="13" t="s">
         <v>19</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="P1" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q1" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="R1" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="S1" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="T1" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="U1" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="V1" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="W1" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="X1" s="13" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:31" ht="15" customHeight="1">
